--- a/data/trans_camb/IP22_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 12,64</t>
+          <t>-6,44; 12,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 0,54</t>
+          <t>-18,28; -0,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 7,34</t>
+          <t>-15,71; 6,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 9,13</t>
+          <t>-8,42; 8,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 0,97</t>
+          <t>-16,81; 0,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 4,43</t>
+          <t>-16,53; 5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 8,64</t>
+          <t>-4,53; 8,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -2,64</t>
+          <t>-16,12; -2,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 1,87</t>
+          <t>-12,92; 2,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 50,15</t>
+          <t>-17,74; 50,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 2,43</t>
+          <t>-50,18; -0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 27,27</t>
+          <t>-43,82; 25,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 42,18</t>
+          <t>-27,02; 38,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 4,76</t>
+          <t>-53,14; 2,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 20,59</t>
+          <t>-53,52; 22,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 34,25</t>
+          <t>-13,48; 32,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,25; -9,82</t>
+          <t>-49,47; -10,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 7,3</t>
+          <t>-40,77; 8,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 18,2</t>
+          <t>5,17; 18,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,29</t>
+          <t>-5,4; 6,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 1,31</t>
+          <t>-12,44; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 15,12</t>
+          <t>2,07; 16,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -4,84</t>
+          <t>-16,37; -4,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -2,75</t>
+          <t>-17,23; -3,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,24</t>
+          <t>5,42; 15,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -0,96</t>
+          <t>-9,05; -0,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; -3,16</t>
+          <t>-12,52; -3,59</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,52; 107,0</t>
+          <t>23,99; 108,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 43,47</t>
+          <t>-23,57; 41,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 8,48</t>
+          <t>-54,31; 6,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 65,3</t>
+          <t>6,49; 66,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -18,16</t>
+          <t>-54,57; -18,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -10,14</t>
+          <t>-55,92; -14,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,49; 70,54</t>
+          <t>20,37; 70,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,84; -4,24</t>
+          <t>-35,04; -1,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,31; -13,89</t>
+          <t>-48,27; -15,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 4,92</t>
+          <t>-9,08; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 6,79</t>
+          <t>-7,08; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 4,95</t>
+          <t>-9,22; 5,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 10,21</t>
+          <t>-4,54; 9,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,45</t>
+          <t>-5,06; 8,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 8,27</t>
+          <t>-5,61; 8,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 5,03</t>
+          <t>-4,51; 5,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,56</t>
+          <t>-3,75; 5,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,91</t>
+          <t>-4,64; 4,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 39,63</t>
+          <t>-43,1; 46,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 54,61</t>
+          <t>-34,61; 53,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 42,47</t>
+          <t>-45,96; 43,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 91,57</t>
+          <t>-25,0; 83,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 74,18</t>
+          <t>-28,35; 75,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 69,76</t>
+          <t>-32,53; 66,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 41,5</t>
+          <t>-25,63; 38,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 43,79</t>
+          <t>-21,01; 42,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 39,37</t>
+          <t>-26,62; 35,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 3,05</t>
+          <t>-8,47; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 3,14</t>
+          <t>-7,94; 3,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 8,05</t>
+          <t>-5,27; 8,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,95</t>
+          <t>0,65; 14,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 5,9</t>
+          <t>-6,86; 5,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 1,77</t>
+          <t>-9,38; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,6</t>
+          <t>-1,66; 7,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,66</t>
+          <t>-5,55; 2,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,16</t>
+          <t>-5,98; 2,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 28,53</t>
+          <t>-52,08; 30,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 31,29</t>
+          <t>-50,59; 28,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 72,56</t>
+          <t>-33,49; 76,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 105,97</t>
+          <t>2,82; 108,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 42,18</t>
+          <t>-37,06; 38,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 13,79</t>
+          <t>-48,25; 12,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 50,33</t>
+          <t>-9,76; 52,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 20,0</t>
+          <t>-34,17; 20,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 21,9</t>
+          <t>-35,04; 24,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,8</t>
+          <t>0,53; 7,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,81</t>
+          <t>-4,98; 1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,04</t>
+          <t>-7,44; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,54</t>
+          <t>2,42; 9,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,6</t>
+          <t>-8,24; -2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -2,94</t>
+          <t>-10,1; -3,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,0</t>
+          <t>2,64; 7,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -1,04</t>
+          <t>-5,62; -0,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,53</t>
+          <t>-7,64; -2,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,34; 43,94</t>
+          <t>3,03; 45,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 10,79</t>
+          <t>-23,77; 9,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 0,63</t>
+          <t>-36,19; 1,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,59; 47,74</t>
+          <t>10,12; 46,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,27; -8,01</t>
+          <t>-35,32; -10,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -14,47</t>
+          <t>-42,06; -15,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,85; 41,84</t>
+          <t>12,21; 39,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -5,24</t>
+          <t>-25,87; -4,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -12,33</t>
+          <t>-35,75; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP22_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,16</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-5,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>-5,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 12,8</t>
+          <t>-8,61; 9,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -0,42</t>
+          <t>-16,81; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 6,74</t>
+          <t>-16,32; 3,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 8,51</t>
+          <t>-5,0; 13,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 0,5</t>
+          <t>-18,2; -0,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 5,18</t>
+          <t>-15,72; 6,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,56</t>
+          <t>-4,73; 8,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; -2,73</t>
+          <t>-15,69; -2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 2,24</t>
+          <t>-13,38; 2,27</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-29,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-24,17%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>11,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-30,25%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-15,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-29,66%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,62%</t>
+          <t>-17,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,54%</t>
+          <t>-20,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 50,12</t>
+          <t>-26,7; 43,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,18; -0,73</t>
+          <t>-54,13; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 25,08</t>
+          <t>-52,18; 14,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 38,13</t>
+          <t>-13,71; 52,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 2,47</t>
+          <t>-49,1; -0,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 22,31</t>
+          <t>-44,02; 29,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 32,22</t>
+          <t>-14,93; 33,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -10,15</t>
+          <t>-47,64; -10,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 8,96</t>
+          <t>-41,74; 9,4</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-10,81</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-10,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-10,81</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,04</t>
+          <t>-6,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-8,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 18,14</t>
+          <t>1,6; 15,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 6,96</t>
+          <t>-16,23; -4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 0,69</t>
+          <t>-17,36; -4,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 16,1</t>
+          <t>5,49; 17,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -4,27</t>
+          <t>-4,8; 6,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -3,58</t>
+          <t>-12,29; 0,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,21</t>
+          <t>5,66; 14,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,27</t>
+          <t>-9,03; -1,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,52; -3,59</t>
+          <t>-13,19; -4,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-39,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-39,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>57,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-29,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-39,8%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,94%</t>
+          <t>-32,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,37%</t>
+          <t>-36,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,99; 108,55</t>
+          <t>5,28; 64,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 41,14</t>
+          <t>-54,25; -20,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 6,35</t>
+          <t>-58,43; -15,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 66,72</t>
+          <t>23,4; 102,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,57; -18,04</t>
+          <t>-21,82; 40,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,92; -14,46</t>
+          <t>-54,26; 2,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 70,71</t>
+          <t>21,05; 68,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -1,26</t>
+          <t>-35,29; -4,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; -15,25</t>
+          <t>-51,65; -19,02</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,35</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,39</t>
+          <t>-4,53; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 6,86</t>
+          <t>-4,93; 8,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 5,34</t>
+          <t>-5,57; 8,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 9,46</t>
+          <t>-9,33; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 8,6</t>
+          <t>-6,92; 6,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,05</t>
+          <t>-8,82; 5,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,1</t>
+          <t>-4,49; 4,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,51</t>
+          <t>-3,59; 5,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,95</t>
+          <t>-5,4; 4,52</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-12,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-2,1%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>-10,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 46,33</t>
+          <t>-25,17; 89,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 53,89</t>
+          <t>-27,5; 79,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 43,75</t>
+          <t>-30,5; 78,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 83,35</t>
+          <t>-44,95; 40,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 75,83</t>
+          <t>-34,81; 52,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 66,03</t>
+          <t>-44,06; 43,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 38,84</t>
+          <t>-25,34; 37,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 42,28</t>
+          <t>-20,57; 43,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 35,96</t>
+          <t>-29,62; 34,33</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,75</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,04</t>
+          <t>0,64; 14,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,0</t>
+          <t>-6,75; 5,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 8,36</t>
+          <t>-9,45; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 14,87</t>
+          <t>-7,81; 2,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 5,39</t>
+          <t>-7,82; 3,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 1,55</t>
+          <t>-4,83; 6,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,05</t>
+          <t>-1,72; 6,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,74</t>
+          <t>-5,13; 2,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,92</t>
+          <t>-5,78; 2,36</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-4,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,81%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-18,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-16,26%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-4,07%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,55%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,81%</t>
+          <t>-10,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 30,91</t>
+          <t>3,26; 108,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 28,23</t>
+          <t>-36,16; 44,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 76,19</t>
+          <t>-51,09; 14,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,82; 108,58</t>
+          <t>-48,66; 27,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 38,7</t>
+          <t>-49,46; 28,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 12,64</t>
+          <t>-28,99; 61,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 52,33</t>
+          <t>-10,42; 50,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 20,16</t>
+          <t>-31,15; 21,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 24,91</t>
+          <t>-34,07; 18,29</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,99</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,66</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,72</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,8</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,88</t>
+          <t>2,42; 9,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,57</t>
+          <t>-8,45; -1,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,4</t>
+          <t>-9,87; -2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,52</t>
+          <t>0,78; 7,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -2,03</t>
+          <t>-5,13; 1,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -3,14</t>
+          <t>-7,66; -0,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,72</t>
+          <t>2,28; 7,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,92</t>
+          <t>-5,78; -1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -2,45</t>
+          <t>-7,96; -2,84</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-22,97%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,64%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>22,13%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-8,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,66%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-22,97%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,43%</t>
+          <t>-21,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,99%</t>
+          <t>-26,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,03; 45,74</t>
+          <t>10,04; 46,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 9,31</t>
+          <t>-35,6; -8,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 1,46</t>
+          <t>-42,17; -14,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,12; 46,98</t>
+          <t>3,46; 43,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,32; -10,08</t>
+          <t>-24,9; 7,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,06; -15,21</t>
+          <t>-35,97; -4,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,21; 39,42</t>
+          <t>10,12; 39,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,87; -4,76</t>
+          <t>-26,27; -5,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,75; -12,64</t>
+          <t>-36,19; -14,46</t>
         </is>
       </c>
     </row>
